--- a/exports/templates/importacion/template_importacion_grupos_minimo.xlsx
+++ b/exports/templates/importacion/template_importacion_grupos_minimo.xlsx
@@ -12,26 +12,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Semestre</t>
+  </si>
   <si>
     <t>Curso</t>
   </si>
   <si>
-    <t>ID Clase</t>
+    <t>Horas anuales</t>
+  </si>
+  <si>
+    <t>Codigo</t>
+  </si>
+  <si>
+    <t>Cupo</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Ingenieria Informatica 2026</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>Programacion 1</t>
   </si>
   <si>
+    <t>96</t>
+  </si>
+  <si>
     <t>INF-101</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>#2563EB</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Fisica 2</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>FIS-201</t>
   </si>
   <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>#16A34A</t>
+  </si>
+  <si>
     <t>Template: Importacion grupos (Minimo)</t>
   </si>
   <si>
@@ -62,13 +104,28 @@
     <t>Estado</t>
   </si>
   <si>
+    <t>Plan combinado. Ej: Ingenieria Informatica 2026</t>
+  </si>
+  <si>
+    <t>Obligatorio</t>
+  </si>
+  <si>
+    <t>Numero de semestre. Ej: 1</t>
+  </si>
+  <si>
     <t>Nombre de materia</t>
   </si>
   <si>
-    <t>Obligatorio</t>
-  </si>
-  <si>
-    <t>Codigo unico del grupo</t>
+    <t>Alias DB de horas (grupos.horas_anuales)</t>
+  </si>
+  <si>
+    <t>Alias DB de ID Clase (grupos.codigo)</t>
+  </si>
+  <si>
+    <t>Cantidad maxima</t>
+  </si>
+  <si>
+    <t>Color del grupo. Ej: #2563EB</t>
   </si>
 </sst>
 </file>
@@ -474,34 +531,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="1" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -512,7 +616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -522,44 +626,44 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -567,10 +671,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -578,10 +682,65 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
